--- a/registers/Master_Citations.xlsx
+++ b/registers/Master_Citations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="723">
   <si>
     <t>Citation Key</t>
   </si>
@@ -412,6 +412,9 @@
     <t>C118</t>
   </si>
   <si>
+    <t>C119</t>
+  </si>
+  <si>
     <t>Va. Code SS10.1-1197.5 (HB508/SB340, enacted 2026, eff. July 1, 2026); Virginia Acts of Assembly 2026 Session, Ch. 156</t>
   </si>
   <si>
@@ -769,6 +772,9 @@
     <t>Solar Energy Industries Association. Land use for utility-scale solar: 5-7 acres per MW of generating capacity.</t>
   </si>
   <si>
+    <t>North American Electric Reliability Corporation (2026). Risk Mitigation for Emerging Large Loads. NERC Reliability Guideline.</t>
+  </si>
+  <si>
     <t>Statute</t>
   </si>
   <si>
@@ -1021,6 +1027,9 @@
     <t>Industry body</t>
   </si>
   <si>
+    <t>Reliability guideline</t>
+  </si>
+  <si>
     <t>VA agrivoltaics legal definition - all six defining criteria (i)-(vi) verified verbatim</t>
   </si>
   <si>
@@ -1378,6 +1387,9 @@
     <t>Adopted as this analysis land-use basis, replacing a project-assembled 4-6 acres/MW. Independently reproduced by the ASGA 2024 census (129,000 acres over 18,000-26,000 MW implies 5.0-7.2) and used as the costing reference by the 2025 Frontiers northeastern grazing study. NREL gives 5.9 for both conventional and grazed tracking.</t>
   </si>
   <si>
+    <t>Resource adequacy should be characterised by MULTIPLE probabilistic metrics -- "loss of load hours, expected unserved energy, and conditional value at risk" -- giving "the duration, magnitude, and severity of potential shortfall events". Explicitly warns that "aggregate metrics like loss of load expectation cannot detect" rare severe outages, so LOLE alone is inadequate. Asks for "thousands of integrated weather, load, and generation scenarios". Basis of lp_package/reliability_metrics. Its Chapter 3 guidance on large-load operational flexibility -- firm vs flexible components, time-varying limits such as AI training windows -- is directly the deferred data-centre axis. Appendix A omits the Resource Planner from its role matrix while Chapter 3 addresses resource adequacy to RPs throughout.</t>
+  </si>
+  <si>
     <t>agrivoltaics; C.1-siting-types</t>
   </si>
   <si>
@@ -1564,6 +1576,9 @@
     <t>land-use; solar-siting</t>
   </si>
   <si>
+    <t>resource-adequacy; reliability-metrics</t>
+  </si>
+  <si>
     <t>VCEA</t>
   </si>
   <si>
@@ -1633,6 +1648,9 @@
     <t>agrivoltaics; acreage</t>
   </si>
   <si>
+    <t>large-loads; data-centres</t>
+  </si>
+  <si>
     <t>regulatory-filing</t>
   </si>
   <si>
@@ -1678,6 +1696,9 @@
     <t>industry standard figure</t>
   </si>
   <si>
+    <t>industry reliability guideline</t>
+  </si>
+  <si>
     <t>econometric-regression</t>
   </si>
   <si>
@@ -1720,6 +1741,9 @@
     <t>generating-capacity basis</t>
   </si>
   <si>
+    <t>probabilistic resource adequacy</t>
+  </si>
+  <si>
     <t>session2</t>
   </si>
   <si>
@@ -2135,6 +2159,9 @@
   </si>
   <si>
     <t>https://docs.nrel.gov/docs/fy24osti/90300.pdf</t>
+  </si>
+  <si>
+    <t>https://www.nerc.com/globalassets/our-work/guidelines/reliability/RG_Risk-Mitigation-For-Emerging-Large-Loads.pdf</t>
   </si>
   <si>
     <t>No URL recovered from source transcripts</t>
@@ -2500,7 +2527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2549,34 +2576,34 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="G2" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="H2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J2" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K2" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2584,31 +2611,31 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F3" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="H3" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J3" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K3" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2616,34 +2643,34 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="G4" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="H4" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J4" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K4" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2651,31 +2678,31 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="H5" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J5" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K5" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="M5" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2683,34 +2710,34 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F6" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G6" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H6" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J6" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K6" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2718,31 +2745,31 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D7">
         <v>2023</v>
       </c>
       <c r="E7" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H7" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J7" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K7" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2750,28 +2777,28 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F8" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J8" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K8" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -2779,31 +2806,31 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D9">
         <v>2023</v>
       </c>
       <c r="E9" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F9" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H9" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J9" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K9" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2811,31 +2838,31 @@
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F10" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H10" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J10" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K10" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2843,31 +2870,31 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D11">
         <v>2026</v>
       </c>
       <c r="E11" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F11" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H11" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J11" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2875,31 +2902,31 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D12">
         <v>2026</v>
       </c>
       <c r="E12" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F12" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H12" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J12" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K12" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="M12" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -2907,31 +2934,31 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D13">
         <v>2023</v>
       </c>
       <c r="E13" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F13" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H13" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J13" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K13" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -2939,31 +2966,31 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D14">
         <v>2026</v>
       </c>
       <c r="E14" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F14" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H14" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J14" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K14" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -2971,28 +2998,28 @@
         <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="E15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F15" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J15" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K15" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="M15" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -3000,31 +3027,31 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F16" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H16" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J16" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K16" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="M16" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3032,34 +3059,34 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D17">
         <v>2026</v>
       </c>
       <c r="E17" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F17" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="G17" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H17" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J17" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K17" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="M17" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3067,37 +3094,37 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D18">
         <v>2026</v>
       </c>
       <c r="E18" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F18" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="G18" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="H18" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="I18" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="J18" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K18" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -3105,31 +3132,31 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D19">
         <v>2026</v>
       </c>
       <c r="E19" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F19" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="H19" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J19" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="K19" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M19" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -3137,31 +3164,31 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D20">
         <v>2026</v>
       </c>
       <c r="E20" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F20" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H20" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J20" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K20" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="M20" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -3169,31 +3196,31 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D21">
         <v>2026</v>
       </c>
       <c r="E21" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F21" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="H21" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J21" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K21" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -3201,31 +3228,31 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D22">
         <v>2026</v>
       </c>
       <c r="E22" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F22" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="H22" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J22" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K22" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -3233,31 +3260,31 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D23">
         <v>2012</v>
       </c>
       <c r="E23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F23" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H23" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J23" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K23" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -3265,31 +3292,31 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24">
         <v>2026</v>
       </c>
       <c r="E24" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F24" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H24" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J24" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K24" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -3297,34 +3324,34 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D25">
         <v>2026</v>
       </c>
       <c r="E25" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F25" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H25" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J25" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K25" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="M25" t="s">
-        <v>708</v>
+        <v>717</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -3332,31 +3359,31 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D26">
         <v>2018</v>
       </c>
       <c r="E26" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F26" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H26" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J26" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K26" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M26" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -3364,31 +3391,31 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D27">
         <v>2026</v>
       </c>
       <c r="E27" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F27" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H27" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J27" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K27" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="M27" t="s">
-        <v>709</v>
+        <v>718</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -3396,31 +3423,31 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C28" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D28">
         <v>2023</v>
       </c>
       <c r="E28" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F28" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H28" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J28" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K28" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -3428,34 +3455,34 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C29" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D29">
         <v>2024</v>
       </c>
       <c r="E29" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="F29" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G29" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H29" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J29" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K29" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -3463,31 +3490,31 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D30">
         <v>2014</v>
       </c>
       <c r="E30" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="F30" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="H30" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J30" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K30" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -3495,31 +3522,31 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C31" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D31">
         <v>2022</v>
       </c>
       <c r="E31" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="F31" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H31" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J31" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K31" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -3527,34 +3554,34 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C32" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D32">
         <v>2019</v>
       </c>
       <c r="E32" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F32" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G32" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="H32" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J32" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K32" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -3562,34 +3589,34 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C33" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D33">
         <v>2019</v>
       </c>
       <c r="E33" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F33" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G33" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="H33" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J33" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K33" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="M33" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -3597,31 +3624,31 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D34">
         <v>2026</v>
       </c>
       <c r="E34" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F34" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H34" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J34" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K34" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -3629,31 +3656,31 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D35">
         <v>2021</v>
       </c>
       <c r="E35" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="F35" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H35" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J35" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K35" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -3661,31 +3688,31 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C36" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D36">
         <v>2023</v>
       </c>
       <c r="E36" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="F36" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="H36" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J36" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K36" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M36" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -3693,34 +3720,34 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D37">
         <v>2026</v>
       </c>
       <c r="E37" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F37" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H37" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I37" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="J37" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K37" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -3728,34 +3755,34 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D38">
         <v>2020</v>
       </c>
       <c r="E38" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="F38" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="H38" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I38" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="J38" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K38" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -3763,34 +3790,34 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D39">
         <v>2019</v>
       </c>
       <c r="E39" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F39" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="G39" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="H39" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J39" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K39" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M39" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -3798,34 +3825,34 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D40">
         <v>2026</v>
       </c>
       <c r="E40" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F40" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H40" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I40" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="J40" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K40" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M40" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -3833,31 +3860,31 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D41">
         <v>2022</v>
       </c>
       <c r="E41" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F41" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="H41" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J41" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K41" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -3865,31 +3892,31 @@
         <v>53</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C42" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D42">
         <v>2026</v>
       </c>
       <c r="E42" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F42" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H42" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J42" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K42" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M42" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -3897,31 +3924,31 @@
         <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C43" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D43">
         <v>2026</v>
       </c>
       <c r="E43" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="F43" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="H43" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J43" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K43" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="M43" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -3929,31 +3956,31 @@
         <v>55</v>
       </c>
       <c r="B44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C44" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D44">
         <v>2026</v>
       </c>
       <c r="E44" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F44" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H44" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J44" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K44" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M44" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -3961,31 +3988,31 @@
         <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C45" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D45">
         <v>2022</v>
       </c>
       <c r="E45" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F45" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H45" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J45" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="K45" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="M45" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -3993,31 +4020,31 @@
         <v>57</v>
       </c>
       <c r="B46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D46">
         <v>2026</v>
       </c>
       <c r="E46" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F46" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="H46" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J46" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="K46" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M46" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -4025,31 +4052,31 @@
         <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C47" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D47">
         <v>2020</v>
       </c>
       <c r="E47" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="F47" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H47" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J47" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="K47" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="M47" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -4057,31 +4084,31 @@
         <v>59</v>
       </c>
       <c r="B48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C48" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D48">
         <v>2026</v>
       </c>
       <c r="E48" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F48" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H48" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J48" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K48" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -4089,31 +4116,31 @@
         <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D49">
         <v>2026</v>
       </c>
       <c r="E49" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F49" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H49" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J49" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K49" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -4121,31 +4148,31 @@
         <v>61</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C50" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D50">
         <v>2026</v>
       </c>
       <c r="E50" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="F50" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H50" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J50" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K50" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -4153,31 +4180,31 @@
         <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C51" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D51">
         <v>2026</v>
       </c>
       <c r="E51" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F51" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H51" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J51" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K51" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -4185,31 +4212,31 @@
         <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D52">
         <v>2026</v>
       </c>
       <c r="E52" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="F52" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H52" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J52" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K52" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -4217,31 +4244,31 @@
         <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D53">
         <v>2025</v>
       </c>
       <c r="E53" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F53" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H53" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J53" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K53" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="M53" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -4249,31 +4276,31 @@
         <v>65</v>
       </c>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D54">
         <v>2026</v>
       </c>
       <c r="E54" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F54" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H54" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J54" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K54" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -4281,34 +4308,34 @@
         <v>66</v>
       </c>
       <c r="B55" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D55">
         <v>2025</v>
       </c>
       <c r="E55" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F55" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G55" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H55" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J55" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K55" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -4316,31 +4343,31 @@
         <v>67</v>
       </c>
       <c r="B56" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D56">
         <v>2025</v>
       </c>
       <c r="E56" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F56" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H56" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J56" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K56" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M56" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -4348,31 +4375,31 @@
         <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D57">
         <v>2026</v>
       </c>
       <c r="E57" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F57" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="H57" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J57" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K57" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="M57" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -4380,31 +4407,31 @@
         <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D58">
         <v>2026</v>
       </c>
       <c r="E58" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F58" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="H58" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J58" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K58" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="M58" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -4412,31 +4439,31 @@
         <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C59" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D59">
         <v>2018</v>
       </c>
       <c r="E59" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F59" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H59" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J59" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K59" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="M59" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -4444,31 +4471,31 @@
         <v>71</v>
       </c>
       <c r="B60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C60" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D60">
         <v>2026</v>
       </c>
       <c r="E60" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F60" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H60" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J60" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K60" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M60" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -4476,31 +4503,31 @@
         <v>72</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C61" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D61">
         <v>2026</v>
       </c>
       <c r="E61" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F61" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H61" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J61" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K61" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="M61" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -4508,31 +4535,31 @@
         <v>73</v>
       </c>
       <c r="B62" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C62" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D62">
         <v>2026</v>
       </c>
       <c r="E62" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="F62" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H62" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J62" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K62" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -4540,31 +4567,31 @@
         <v>74</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D63">
         <v>2026</v>
       </c>
       <c r="E63" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F63" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H63" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J63" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K63" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="M63" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -4572,31 +4599,31 @@
         <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C64" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D64">
         <v>2025</v>
       </c>
       <c r="E64" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F64" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H64" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J64" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K64" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="M64" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="65" spans="1:13">
@@ -4604,31 +4631,31 @@
         <v>76</v>
       </c>
       <c r="B65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C65" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D65">
         <v>2025</v>
       </c>
       <c r="E65" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F65" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H65" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J65" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K65" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="M65" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -4636,34 +4663,34 @@
         <v>77</v>
       </c>
       <c r="B66" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C66" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D66">
         <v>2026</v>
       </c>
       <c r="E66" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F66" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G66" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="I66" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="J66" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K66" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="M66" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="67" spans="1:13">
@@ -4671,31 +4698,31 @@
         <v>78</v>
       </c>
       <c r="B67" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C67" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D67">
         <v>2026</v>
       </c>
       <c r="E67" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F67" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H67" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J67" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K67" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="M67" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="68" spans="1:13">
@@ -4703,31 +4730,31 @@
         <v>79</v>
       </c>
       <c r="B68" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C68" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D68">
         <v>2026</v>
       </c>
       <c r="E68" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F68" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H68" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J68" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K68" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M68" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="69" spans="1:13">
@@ -4735,31 +4762,31 @@
         <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C69" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D69">
         <v>2026</v>
       </c>
       <c r="E69" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F69" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H69" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J69" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K69" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="M69" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="70" spans="1:13">
@@ -4767,31 +4794,31 @@
         <v>81</v>
       </c>
       <c r="B70" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C70" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D70">
         <v>2026</v>
       </c>
       <c r="E70" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F70" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="H70" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J70" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K70" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="M70" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -4799,31 +4826,31 @@
         <v>82</v>
       </c>
       <c r="B71" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C71" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D71">
         <v>2026</v>
       </c>
       <c r="E71" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F71" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H71" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J71" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K71" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="M71" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="72" spans="1:13">
@@ -4831,31 +4858,31 @@
         <v>83</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C72" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D72">
         <v>2026</v>
       </c>
       <c r="E72" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F72" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H72" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J72" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K72" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="M72" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="73" spans="1:13">
@@ -4863,37 +4890,37 @@
         <v>84</v>
       </c>
       <c r="B73" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C73" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D73">
         <v>2026</v>
       </c>
       <c r="E73" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F73" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G73" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="H73" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J73" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K73" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="M73" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
     </row>
     <row r="74" spans="1:13">
@@ -4901,34 +4928,34 @@
         <v>85</v>
       </c>
       <c r="B74" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C74" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D74">
         <v>2026</v>
       </c>
       <c r="E74" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F74" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="G74" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="H74" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J74" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K74" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M74" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="75" spans="1:13">
@@ -4936,34 +4963,34 @@
         <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C75" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D75">
         <v>2024</v>
       </c>
       <c r="E75" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F75" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H75" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J75" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K75" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="M75" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="76" spans="1:13">
@@ -4971,31 +4998,31 @@
         <v>87</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D76">
         <v>2026</v>
       </c>
       <c r="E76" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F76" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H76" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J76" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="K76" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="M76" t="s">
-        <v>711</v>
+        <v>720</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -5003,28 +5030,28 @@
         <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C77" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D77">
         <v>2026</v>
       </c>
       <c r="E77" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="F77" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J77" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K77" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="M77" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -5032,31 +5059,31 @@
         <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C78" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D78">
         <v>2026</v>
       </c>
       <c r="E78" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F78" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H78" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J78" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K78" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -5064,22 +5091,22 @@
         <v>90</v>
       </c>
       <c r="B79" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C79" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D79">
         <v>2026</v>
       </c>
       <c r="E79" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J79" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K79" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
     </row>
     <row r="80" spans="1:13">
@@ -5087,31 +5114,31 @@
         <v>91</v>
       </c>
       <c r="B80" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C80" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D80">
         <v>2024</v>
       </c>
       <c r="E80" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F80" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="H80" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J80" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K80" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
     </row>
     <row r="81" spans="1:13">
@@ -5119,31 +5146,31 @@
         <v>92</v>
       </c>
       <c r="B81" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C81" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D81">
         <v>2000</v>
       </c>
       <c r="E81" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F81" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H81" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J81" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K81" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="82" spans="1:13">
@@ -5151,31 +5178,31 @@
         <v>93</v>
       </c>
       <c r="B82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C82" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D82">
         <v>2025</v>
       </c>
       <c r="E82" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F82" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="H82" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J82" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K82" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M82" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="83" spans="1:13">
@@ -5183,37 +5210,37 @@
         <v>94</v>
       </c>
       <c r="B83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D83">
         <v>2026</v>
       </c>
       <c r="E83" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F83" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G83" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H83" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J83" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="K83" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="M83" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="84" spans="1:13">
@@ -5221,31 +5248,31 @@
         <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C84" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D84">
         <v>2026</v>
       </c>
       <c r="E84" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F84" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H84" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J84" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="K84" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="M84" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="85" spans="1:13">
@@ -5253,31 +5280,31 @@
         <v>96</v>
       </c>
       <c r="B85" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C85" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D85">
         <v>2024</v>
       </c>
       <c r="E85" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F85" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H85" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J85" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K85" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
     </row>
     <row r="86" spans="1:13">
@@ -5285,31 +5312,31 @@
         <v>97</v>
       </c>
       <c r="B86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C86" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D86">
         <v>2022</v>
       </c>
       <c r="E86" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F86" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H86" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J86" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="K86" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
     </row>
     <row r="87" spans="1:13">
@@ -5317,31 +5344,31 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C87" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D87">
         <v>2026</v>
       </c>
       <c r="E87" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F87" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H87" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J87" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="K87" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="M87" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="88" spans="1:13">
@@ -5349,31 +5376,31 @@
         <v>99</v>
       </c>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C88" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D88">
         <v>2026</v>
       </c>
       <c r="E88" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F88" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="H88" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J88" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K88" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="M88" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="89" spans="1:13">
@@ -5381,28 +5408,28 @@
         <v>100</v>
       </c>
       <c r="B89" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C89" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D89">
         <v>2026</v>
       </c>
       <c r="E89" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F89" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J89" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K89" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="M89" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="90" spans="1:13">
@@ -5410,28 +5437,28 @@
         <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C90" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D90">
         <v>2018</v>
       </c>
       <c r="E90" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F90" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J90" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K90" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="M90" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="91" spans="1:13">
@@ -5439,31 +5466,31 @@
         <v>102</v>
       </c>
       <c r="B91" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C91" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D91">
         <v>2023</v>
       </c>
       <c r="E91" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F91" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H91" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J91" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K91" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="M91" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="92" spans="1:13">
@@ -5471,31 +5498,31 @@
         <v>103</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C92" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D92">
         <v>2026</v>
       </c>
       <c r="E92" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F92" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="H92" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="J92" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K92" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M92" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="93" spans="1:13">
@@ -5503,31 +5530,31 @@
         <v>104</v>
       </c>
       <c r="B93" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C93" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D93">
         <v>2026</v>
       </c>
       <c r="E93" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="F93" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H93" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J93" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K93" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="M93" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="94" spans="1:13">
@@ -5535,31 +5562,31 @@
         <v>105</v>
       </c>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C94" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D94">
         <v>2026</v>
       </c>
       <c r="E94" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F94" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H94" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J94" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K94" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
     </row>
     <row r="95" spans="1:13">
@@ -5567,22 +5594,22 @@
         <v>106</v>
       </c>
       <c r="B95" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D95">
         <v>2026</v>
       </c>
       <c r="E95" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J95" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K95" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
     </row>
     <row r="96" spans="1:13">
@@ -5590,28 +5617,28 @@
         <v>107</v>
       </c>
       <c r="B96" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C96" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D96">
         <v>2026</v>
       </c>
       <c r="E96" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F96" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J96" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="K96" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="M96" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="97" spans="1:13">
@@ -5619,22 +5646,22 @@
         <v>108</v>
       </c>
       <c r="B97" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C97" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D97">
         <v>2026</v>
       </c>
       <c r="E97" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J97" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K97" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="98" spans="1:13">
@@ -5642,22 +5669,22 @@
         <v>109</v>
       </c>
       <c r="B98" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C98" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D98">
         <v>2026</v>
       </c>
       <c r="E98" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J98" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="K98" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
     </row>
     <row r="99" spans="1:13">
@@ -5665,34 +5692,34 @@
         <v>110</v>
       </c>
       <c r="B99" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C99" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D99">
         <v>2026</v>
       </c>
       <c r="E99" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F99" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G99" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H99" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="J99" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K99" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="M99" t="s">
-        <v>707</v>
+        <v>716</v>
       </c>
     </row>
     <row r="100" spans="1:13">
@@ -5700,22 +5727,22 @@
         <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C100" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D100">
         <v>2026</v>
       </c>
       <c r="E100" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="J100" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K100" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
     </row>
     <row r="101" spans="1:13">
@@ -5723,31 +5750,31 @@
         <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C101" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D101">
         <v>2026</v>
       </c>
       <c r="E101" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F101" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H101" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J101" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="K101" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
     </row>
     <row r="102" spans="1:13">
@@ -5755,34 +5782,34 @@
         <v>113</v>
       </c>
       <c r="B102" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C102" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D102">
         <v>2023</v>
       </c>
       <c r="E102" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F102" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="G102" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H102" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J102" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="K102" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
     </row>
     <row r="103" spans="1:13">
@@ -5790,37 +5817,37 @@
         <v>114</v>
       </c>
       <c r="B103" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C103" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D103">
         <v>2025</v>
       </c>
       <c r="E103" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="F103" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="G103" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="H103" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="I103" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="J103" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="K103" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
     </row>
     <row r="104" spans="1:13">
@@ -5828,34 +5855,34 @@
         <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C104" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D104">
         <v>2015</v>
       </c>
       <c r="E104" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F104" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G104" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H104" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="J104" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="K104" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
     </row>
     <row r="105" spans="1:13">
@@ -5863,37 +5890,37 @@
         <v>116</v>
       </c>
       <c r="B105" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C105" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D105">
         <v>2025</v>
       </c>
       <c r="E105" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F105" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H105" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="I105" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="J105" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="K105" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="M105" t="s">
-        <v>712</v>
+        <v>721</v>
       </c>
     </row>
     <row r="106" spans="1:13">
@@ -5901,34 +5928,34 @@
         <v>117</v>
       </c>
       <c r="B106" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C106" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D106">
         <v>2025</v>
       </c>
       <c r="E106" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F106" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="G106" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H106" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="J106" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="K106" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
     </row>
     <row r="107" spans="1:13">
@@ -5936,34 +5963,34 @@
         <v>118</v>
       </c>
       <c r="B107" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C107" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D107">
         <v>2013</v>
       </c>
       <c r="E107" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F107" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="G107" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="H107" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J107" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="K107" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
     </row>
     <row r="108" spans="1:13">
@@ -5971,34 +5998,34 @@
         <v>119</v>
       </c>
       <c r="B108" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C108" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D108">
         <v>2024</v>
       </c>
       <c r="E108" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F108" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="G108" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H108" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J108" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="K108" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
     </row>
     <row r="109" spans="1:13">
@@ -6006,34 +6033,34 @@
         <v>120</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C109" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D109">
         <v>2026</v>
       </c>
       <c r="E109" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F109" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G109" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H109" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J109" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="K109" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
     </row>
     <row r="110" spans="1:13">
@@ -6041,34 +6068,34 @@
         <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C110" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D110">
         <v>2025</v>
       </c>
       <c r="E110" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F110" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="G110" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H110" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J110" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="K110" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
     </row>
     <row r="111" spans="1:13">
@@ -6076,37 +6103,37 @@
         <v>122</v>
       </c>
       <c r="B111" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C111" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D111">
         <v>2020</v>
       </c>
       <c r="E111" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="F111" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="G111" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="H111" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="I111" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="J111" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K111" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
     </row>
     <row r="112" spans="1:13">
@@ -6114,37 +6141,37 @@
         <v>123</v>
       </c>
       <c r="B112" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D112">
         <v>2013</v>
       </c>
       <c r="E112" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F112" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G112" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H112" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="I112" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="J112" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K112" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
     </row>
     <row r="113" spans="1:13">
@@ -6152,37 +6179,37 @@
         <v>124</v>
       </c>
       <c r="B113" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C113" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D113">
         <v>2018</v>
       </c>
       <c r="E113" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F113" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="G113" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="H113" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="I113" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="J113" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K113" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
     </row>
     <row r="114" spans="1:13">
@@ -6190,37 +6217,37 @@
         <v>125</v>
       </c>
       <c r="B114" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C114" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D114">
         <v>2020</v>
       </c>
       <c r="E114" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F114" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G114" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H114" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="I114" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="J114" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K114" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="M114" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
     </row>
     <row r="115" spans="1:13">
@@ -6228,37 +6255,37 @@
         <v>126</v>
       </c>
       <c r="B115" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C115" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D115">
         <v>2026</v>
       </c>
       <c r="E115" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F115" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G115" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="H115" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="I115" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="J115" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K115" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
     </row>
     <row r="116" spans="1:13">
@@ -6266,37 +6293,37 @@
         <v>127</v>
       </c>
       <c r="B116" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C116" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D116">
         <v>2024</v>
       </c>
       <c r="E116" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F116" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G116" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="H116" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="I116" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="J116" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K116" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="M116" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
     </row>
     <row r="117" spans="1:13">
@@ -6304,37 +6331,37 @@
         <v>128</v>
       </c>
       <c r="B117" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C117" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D117">
         <v>2024</v>
       </c>
       <c r="E117" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="F117" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="G117" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="H117" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="I117" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="J117" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K117" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
     </row>
     <row r="118" spans="1:13">
@@ -6342,37 +6369,37 @@
         <v>129</v>
       </c>
       <c r="B118" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C118" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D118">
         <v>2010</v>
       </c>
       <c r="E118" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F118" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G118" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="H118" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="I118" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="J118" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K118" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="M118" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
     </row>
     <row r="119" spans="1:13">
@@ -6380,37 +6407,37 @@
         <v>130</v>
       </c>
       <c r="B119" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C119" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D119">
         <v>2025</v>
       </c>
       <c r="E119" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F119" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G119" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="H119" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="I119" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="J119" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K119" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="M119" t="s">
-        <v>713</v>
+        <v>722</v>
       </c>
     </row>
     <row r="120" spans="1:13">
@@ -6418,37 +6445,75 @@
         <v>131</v>
       </c>
       <c r="B120" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C120" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D120">
         <v>2024</v>
       </c>
       <c r="E120" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F120" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="G120" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H120" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="I120" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="J120" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="K120" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="M120" t="s">
-        <v>713</v>
+        <v>722</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121" t="s">
+        <v>252</v>
+      </c>
+      <c r="C121" t="s">
+        <v>337</v>
+      </c>
+      <c r="D121">
+        <v>2026</v>
+      </c>
+      <c r="E121" t="s">
+        <v>457</v>
+      </c>
+      <c r="F121" t="s">
+        <v>520</v>
+      </c>
+      <c r="G121" t="s">
+        <v>544</v>
+      </c>
+      <c r="H121" t="s">
+        <v>560</v>
+      </c>
+      <c r="I121" t="s">
+        <v>575</v>
+      </c>
+      <c r="J121" t="s">
+        <v>591</v>
+      </c>
+      <c r="K121" t="s">
+        <v>592</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>715</v>
       </c>
     </row>
   </sheetData>
@@ -6512,6 +6577,7 @@
     <hyperlink ref="L113" r:id="rId57"/>
     <hyperlink ref="L115" r:id="rId58"/>
     <hyperlink ref="L117" r:id="rId59"/>
+    <hyperlink ref="L121" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
